--- a/artfynd/A 48738-2024 artfynd.xlsx
+++ b/artfynd/A 48738-2024 artfynd.xlsx
@@ -4280,7 +4280,7 @@
         <v>133390859</v>
       </c>
       <c r="B33" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>133390861</v>
       </c>
       <c r="B34" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>133390860</v>
       </c>
       <c r="B36" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>133390858</v>
       </c>
       <c r="B37" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48738-2024 artfynd.xlsx
+++ b/artfynd/A 48738-2024 artfynd.xlsx
@@ -4280,7 +4280,7 @@
         <v>133390859</v>
       </c>
       <c r="B33" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>133390861</v>
       </c>
       <c r="B34" t="n">
-        <v>80468</v>
+        <v>80482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>133390856</v>
       </c>
       <c r="B35" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>133390860</v>
       </c>
       <c r="B36" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>133390858</v>
       </c>
       <c r="B37" t="n">
-        <v>80399</v>
+        <v>80413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48738-2024 artfynd.xlsx
+++ b/artfynd/A 48738-2024 artfynd.xlsx
@@ -4280,7 +4280,7 @@
         <v>133390859</v>
       </c>
       <c r="B33" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>133390861</v>
       </c>
       <c r="B34" t="n">
-        <v>80482</v>
+        <v>80478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>133390856</v>
       </c>
       <c r="B35" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>133390860</v>
       </c>
       <c r="B36" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>133390858</v>
       </c>
       <c r="B37" t="n">
-        <v>80413</v>
+        <v>80423</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 48738-2024 artfynd.xlsx
+++ b/artfynd/A 48738-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334126</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334128</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334117</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334118</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334120</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334121</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334124</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334135</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334136</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334138</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334139</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2185,6 +2260,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334150</t>
         </is>
       </c>
     </row>
@@ -2297,6 +2377,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133390859</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133390860</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334115</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334116</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2710,6 +2810,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334119</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2811,6 +2916,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334134</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3022,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334140</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3011,6 +3126,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334149</t>
         </is>
       </c>
     </row>
@@ -3123,6 +3243,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133390861</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3233,6 +3358,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133390862</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3339,6 +3469,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334129</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3443,6 +3578,11 @@
       <c r="AY28" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334144</t>
         </is>
       </c>
     </row>
@@ -3565,6 +3705,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133390856</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3666,6 +3811,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334137</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3767,6 +3917,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334111</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3868,6 +4023,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334141</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3969,6 +4129,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334148</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4070,6 +4235,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334107</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4171,6 +4341,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334131</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4272,6 +4447,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334147</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4373,6 +4553,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334108</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4468,6 +4653,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95334122</t>
         </is>
       </c>
     </row>
@@ -4580,6 +4770,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133390857</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4690,8 +4885,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133390858</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>